--- a/04_DESIGN_TABLES/DesignTable_5504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5504_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -693,13 +693,13 @@
         <v>0.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         <v>0.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         <v>0.375</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         <v>0.655</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_5504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,104 +1013,104 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5504-12-12-FG</t>
+          <t>5504-06-04-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="C5" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="J5" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="K5" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="M5" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="N5" t="n">
-        <v>0.51214</v>
+        <v>0.32944</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="T5" t="n">
-        <v>0.51214</v>
+        <v>0.25944</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>0.875</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="X5" t="n">
-        <v>1.31</v>
+        <v>0.875</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.655</v>
+        <v>0.4375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.37766</v>
+        <v>0.25209</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.37766</v>
+        <v>0.25209</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.75583</v>
+        <v>0.50468</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5504-12-12-FG</t>
+          <t>5504-06-04-FG</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90 deg Female Pipe Elbow, 3/4-14 NPTF (female) x 3/4-14 NPTF (female)</t>
+          <t>90 deg Female Pipe Elbow, 3/8-18 NPTF (female) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1135,146 +1135,702 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Air-Way s129 only (double-pass 22 rows); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "N1 LGTH" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 3/8-18, A2 NPTF 1/4-18) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5504-12-12-FG</t>
+          <t>5504-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>5504-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>5504-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 3/8-18 NPTF (female) x 3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "N1 LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 3/8-18, A2 NPTF 3/8-18) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5504-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5504-08-06-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>5504-08-06-FG</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 1/2-14 NPTF (female) x 3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-08-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "N LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "N1 LGTH" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 1/2-14, A2 NPTF 3/8-18) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-08-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>5504-08-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.37766</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.37766</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.75583</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>5504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 3/4-14 NPTF (female) x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Air-Way s129 only (double-pass 22 rows); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>5504-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>5504-16-16-FG</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B9" t="n">
         <v>1.62</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C9" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>1.62</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E9" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F9" t="n">
         <v>1.14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G9" t="n">
         <v>1.62</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H9" t="n">
         <v>1.14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I9" t="n">
         <v>1.62</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J9" t="n">
         <v>1.14</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K9" t="n">
         <v>1.14</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L9" t="n">
         <v>0.08696</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M9" t="n">
         <v>0.57</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N9" t="n">
         <v>0.63957</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O9" t="n">
         <v>1.62</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P9" t="n">
         <v>1.14</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q9" t="n">
         <v>1.14</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R9" t="n">
         <v>0.08696</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S9" t="n">
         <v>0.57</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T9" t="n">
         <v>0.63957</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>1.62</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V9" t="n">
         <v>1.63</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W9" t="n">
         <v>1.36</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X9" t="n">
         <v>1.63</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y9" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z9" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA9" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AB9" t="n">
         <v>0.47004</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC9" t="n">
         <v>0.47004</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD9" t="n">
         <v>0.94058</v>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>5504-16-16-FG</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>90 deg Female Pipe Elbow, 1-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>5504</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>Air-Way s129 only (double-pass 22 rows); female NPTF per ANSI B1.20.3 | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>5504-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5504-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>5504-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>90 deg Female Pipe Elbow, 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "N1 LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "Y FLATS" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPTF 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the tap drill carried to the crossing (ASSUMPTION: Air-Way publishes no bore for this part); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-20-20 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>5504-20-20-FG</t>
         </is>
       </c>
     </row>
